--- a/实体 entity/猪灵交易 1.16.2+.xlsx
+++ b/实体 entity/猪灵交易 1.16.2+.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\实体 entity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBAC97F5-2A40-451E-AADD-3EB3974844F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2DEB62-8388-4498-AE04-7C37647B6B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6860" yWindow="2460" windowWidth="16360" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="猪灵交易" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>物品</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -151,6 +151,27 @@
   <si>
     <t>一盒金块获得
 物品平均数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>下界合金锄</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>诡异菌岩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>失水恶魂</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>曾经存在，后来被移除的，值得注意的几个：</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个物品平均
+需要金块数量</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -159,8 +180,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="177" formatCode="0.000%"/>
-    <numFmt numFmtId="180" formatCode="0.000000"/>
+    <numFmt numFmtId="176" formatCode="0.000%"/>
+    <numFmt numFmtId="177" formatCode="0.000000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -234,16 +255,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -527,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -536,13 +557,13 @@
     <col min="4" max="4" width="8.5" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.6640625" style="1"/>
+    <col min="7" max="8" width="12.33203125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -565,16 +586,19 @@
         <v>24</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -600,19 +624,23 @@
         <v>91.8</v>
       </c>
       <c r="H2" s="6">
+        <f>G2/9</f>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="I2" s="6">
         <f>D2*F2</f>
         <v>1.0893246187363835E-2</v>
       </c>
-      <c r="I2" s="6">
-        <f>1728*H2</f>
+      <c r="J2" s="6">
+        <f>1728*I2</f>
         <v>18.823529411764707</v>
       </c>
-      <c r="J2" s="9">
-        <f>I2*9</f>
+      <c r="K2" s="9">
+        <f>J2*9</f>
         <v>169.41176470588235</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -623,34 +651,38 @@
         <v>1</v>
       </c>
       <c r="D3" s="7">
-        <f t="shared" ref="D3:D19" si="0">(B3+C3)/2</f>
+        <f t="shared" ref="D3:D20" si="0">(B3+C3)/2</f>
         <v>1</v>
       </c>
       <c r="E3" s="7">
         <v>8</v>
       </c>
       <c r="F3" s="8">
-        <f t="shared" ref="F3:F19" si="1">E3/SUM(E$2:E$19)</f>
+        <f t="shared" ref="F3:F20" si="1">E3/SUM(E$2:E$19)</f>
         <v>1.7429193899782137E-2</v>
       </c>
       <c r="G3" s="6">
-        <f t="shared" ref="G3:G19" si="2">1/(D3*F3)</f>
+        <f t="shared" ref="G3:G20" si="2">1/(D3*F3)</f>
         <v>57.374999999999993</v>
       </c>
       <c r="H3" s="6">
-        <f t="shared" ref="H3:H19" si="3">D3*F3</f>
+        <f t="shared" ref="H3:H20" si="3">G3/9</f>
+        <v>6.3749999999999991</v>
+      </c>
+      <c r="I3" s="6">
+        <f>D3*F3</f>
         <v>1.7429193899782137E-2</v>
       </c>
-      <c r="I3" s="6">
-        <f t="shared" ref="I3:I19" si="4">1728*H3</f>
+      <c r="J3" s="6">
+        <f t="shared" ref="J3:J20" si="4">1728*I3</f>
         <v>30.117647058823533</v>
       </c>
-      <c r="J3" s="9">
-        <f t="shared" ref="J3:J19" si="5">I3*9</f>
+      <c r="K3" s="9">
+        <f t="shared" ref="K3:K20" si="5">J3*9</f>
         <v>271.05882352941177</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -677,18 +709,22 @@
       </c>
       <c r="H4" s="6">
         <f t="shared" si="3"/>
+        <v>6.3749999999999991</v>
+      </c>
+      <c r="I4" s="6">
+        <f>D4*F4</f>
         <v>1.7429193899782137E-2</v>
       </c>
-      <c r="I4" s="6">
+      <c r="J4" s="6">
         <f t="shared" si="4"/>
         <v>30.117647058823533</v>
       </c>
-      <c r="J4" s="9">
+      <c r="K4" s="9">
         <f t="shared" si="5"/>
         <v>271.05882352941177</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
@@ -715,18 +751,22 @@
       </c>
       <c r="H5" s="6">
         <f t="shared" si="3"/>
+        <v>6.3749999999999991</v>
+      </c>
+      <c r="I5" s="6">
+        <f>D5*F5</f>
         <v>1.7429193899782137E-2</v>
       </c>
-      <c r="I5" s="6">
+      <c r="J5" s="6">
         <f t="shared" si="4"/>
         <v>30.117647058823533</v>
       </c>
-      <c r="J5" s="9">
+      <c r="K5" s="9">
         <f t="shared" si="5"/>
         <v>271.05882352941177</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
@@ -753,18 +793,22 @@
       </c>
       <c r="H6" s="6">
         <f t="shared" si="3"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I6" s="6">
+        <f>D6*F6</f>
         <v>2.178649237472767E-2</v>
       </c>
-      <c r="I6" s="6">
+      <c r="J6" s="6">
         <f t="shared" si="4"/>
         <v>37.647058823529413</v>
       </c>
-      <c r="J6" s="9">
+      <c r="K6" s="9">
         <f t="shared" si="5"/>
         <v>338.8235294117647</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -791,18 +835,22 @@
       </c>
       <c r="H7" s="6">
         <f t="shared" si="3"/>
+        <v>0.22173913043478258</v>
+      </c>
+      <c r="I7" s="6">
+        <f>D7*F7</f>
         <v>0.50108932461873645</v>
       </c>
-      <c r="I7" s="6">
+      <c r="J7" s="6">
         <f t="shared" si="4"/>
         <v>865.88235294117658</v>
       </c>
-      <c r="J7" s="9">
+      <c r="K7" s="9">
         <f t="shared" si="5"/>
         <v>7792.9411764705892</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
@@ -829,18 +877,22 @@
       </c>
       <c r="H8" s="6">
         <f t="shared" si="3"/>
+        <v>1.7</v>
+      </c>
+      <c r="I8" s="6">
+        <f>D8*F8</f>
         <v>6.535947712418301E-2</v>
       </c>
-      <c r="I8" s="6">
+      <c r="J8" s="6">
         <f t="shared" si="4"/>
         <v>112.94117647058825</v>
       </c>
-      <c r="J8" s="9">
+      <c r="K8" s="9">
         <f t="shared" si="5"/>
         <v>1016.4705882352943</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
@@ -867,18 +919,22 @@
       </c>
       <c r="H9" s="6">
         <f t="shared" si="3"/>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="I9" s="6">
+        <f>D9*F9</f>
         <v>0.26143790849673204</v>
       </c>
-      <c r="I9" s="6">
+      <c r="J9" s="6">
         <f t="shared" si="4"/>
         <v>451.76470588235298</v>
       </c>
-      <c r="J9" s="9">
+      <c r="K9" s="9">
         <f t="shared" si="5"/>
         <v>4065.882352941177</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
@@ -905,18 +961,22 @@
       </c>
       <c r="H10" s="6">
         <f t="shared" si="3"/>
+        <v>0.3</v>
+      </c>
+      <c r="I10" s="6">
+        <f>D10*F10</f>
         <v>0.37037037037037041</v>
       </c>
-      <c r="I10" s="6">
+      <c r="J10" s="6">
         <f t="shared" si="4"/>
         <v>640.00000000000011</v>
       </c>
-      <c r="J10" s="9">
+      <c r="K10" s="9">
         <f t="shared" si="5"/>
         <v>5760.0000000000009</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
@@ -943,18 +1003,22 @@
       </c>
       <c r="H11" s="6">
         <f t="shared" si="3"/>
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="I11" s="6">
+        <f>D11*F11</f>
         <v>8.714596949891068E-2</v>
       </c>
-      <c r="I11" s="6">
+      <c r="J11" s="6">
         <f t="shared" si="4"/>
         <v>150.58823529411765</v>
       </c>
-      <c r="J11" s="9">
+      <c r="K11" s="9">
         <f t="shared" si="5"/>
         <v>1355.2941176470588</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>13</v>
       </c>
@@ -981,18 +1045,22 @@
       </c>
       <c r="H12" s="6">
         <f t="shared" si="3"/>
+        <v>0.63749999999999996</v>
+      </c>
+      <c r="I12" s="6">
+        <f>D12*F12</f>
         <v>0.17429193899782136</v>
       </c>
-      <c r="I12" s="6">
+      <c r="J12" s="6">
         <f t="shared" si="4"/>
         <v>301.1764705882353</v>
       </c>
-      <c r="J12" s="9">
+      <c r="K12" s="9">
         <f t="shared" si="5"/>
         <v>2710.5882352941176</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>14</v>
       </c>
@@ -1019,18 +1087,22 @@
       </c>
       <c r="H13" s="6">
         <f t="shared" si="3"/>
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="I13" s="6">
+        <f>D13*F13</f>
         <v>8.714596949891068E-2</v>
       </c>
-      <c r="I13" s="6">
+      <c r="J13" s="6">
         <f t="shared" si="4"/>
         <v>150.58823529411765</v>
       </c>
-      <c r="J13" s="9">
+      <c r="K13" s="9">
         <f t="shared" si="5"/>
         <v>1355.2941176470588</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>15</v>
       </c>
@@ -1057,18 +1129,22 @@
       </c>
       <c r="H14" s="6">
         <f t="shared" si="3"/>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="I14" s="6">
+        <f>D14*F14</f>
         <v>0.26143790849673204</v>
       </c>
-      <c r="I14" s="6">
+      <c r="J14" s="6">
         <f t="shared" si="4"/>
         <v>451.76470588235298</v>
       </c>
-      <c r="J14" s="9">
+      <c r="K14" s="9">
         <f t="shared" si="5"/>
         <v>4065.882352941177</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>16</v>
       </c>
@@ -1095,18 +1171,22 @@
       </c>
       <c r="H15" s="6">
         <f t="shared" si="3"/>
+        <v>0.255</v>
+      </c>
+      <c r="I15" s="6">
+        <f>D15*F15</f>
         <v>0.4357298474945534</v>
       </c>
-      <c r="I15" s="6">
+      <c r="J15" s="6">
         <f t="shared" si="4"/>
         <v>752.94117647058829</v>
       </c>
-      <c r="J15" s="9">
+      <c r="K15" s="9">
         <f t="shared" si="5"/>
         <v>6776.4705882352946</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -1133,18 +1213,22 @@
       </c>
       <c r="H16" s="6">
         <f t="shared" si="3"/>
+        <v>0.255</v>
+      </c>
+      <c r="I16" s="6">
+        <f>D16*F16</f>
         <v>0.4357298474945534</v>
       </c>
-      <c r="I16" s="6">
+      <c r="J16" s="6">
         <f t="shared" si="4"/>
         <v>752.94117647058829</v>
       </c>
-      <c r="J16" s="9">
+      <c r="K16" s="9">
         <f t="shared" si="5"/>
         <v>6776.4705882352946</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
@@ -1171,18 +1255,22 @@
       </c>
       <c r="H17" s="6">
         <f t="shared" si="3"/>
+        <v>0.14166666666666666</v>
+      </c>
+      <c r="I17" s="6">
+        <f>D17*F17</f>
         <v>0.78431372549019618</v>
       </c>
-      <c r="I17" s="6">
+      <c r="J17" s="6">
         <f t="shared" si="4"/>
         <v>1355.294117647059</v>
       </c>
-      <c r="J17" s="9">
+      <c r="K17" s="9">
         <f t="shared" si="5"/>
         <v>12197.647058823532</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>19</v>
       </c>
@@ -1209,18 +1297,22 @@
       </c>
       <c r="H18" s="6">
         <f t="shared" si="3"/>
+        <v>0.10625</v>
+      </c>
+      <c r="I18" s="6">
+        <f>D18*F18</f>
         <v>1.0457516339869282</v>
       </c>
-      <c r="I18" s="6">
+      <c r="J18" s="6">
         <f t="shared" si="4"/>
         <v>1807.0588235294119</v>
       </c>
-      <c r="J18" s="9">
+      <c r="K18" s="9">
         <f t="shared" si="5"/>
         <v>16263.529411764708</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
@@ -1247,30 +1339,349 @@
       </c>
       <c r="H19" s="6">
         <f t="shared" si="3"/>
+        <v>0.10625</v>
+      </c>
+      <c r="I19" s="6">
+        <f>D19*F19</f>
         <v>1.0457516339869282</v>
       </c>
-      <c r="I19" s="6">
+      <c r="J19" s="6">
         <f t="shared" si="4"/>
         <v>1807.0588235294119</v>
       </c>
-      <c r="J19" s="9">
+      <c r="K19" s="9">
         <f t="shared" si="5"/>
         <v>16263.529411764708</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5" t="str">
-        <f>"总权重："&amp;SUM(E2:E19)</f>
-        <v>总权重：459</v>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="7">
+        <v>1</v>
+      </c>
+      <c r="C20" s="7">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E20" s="7">
+        <v>10</v>
+      </c>
+      <c r="F20" s="8">
+        <f t="shared" si="1"/>
+        <v>2.178649237472767E-2</v>
+      </c>
+      <c r="G20" s="6">
+        <f t="shared" si="2"/>
+        <v>45.9</v>
+      </c>
+      <c r="H20" s="6">
+        <f t="shared" si="3"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I20" s="6">
+        <f>D20*F20</f>
+        <v>2.178649237472767E-2</v>
+      </c>
+      <c r="J20" s="6">
+        <f t="shared" si="4"/>
+        <v>37.647058823529413</v>
+      </c>
+      <c r="K20" s="9">
+        <f t="shared" si="5"/>
+        <v>338.8235294117647</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5" t="str">
+        <f>"总权重："&amp;SUM(E2:E20)</f>
+        <v>总权重：469</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="7">
+        <v>1</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7">
+        <f>(B24+C24)/2</f>
+        <v>1</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8">
+        <f>E24/SUM(E$2:E$19)</f>
+        <v>2.1786492374727671E-3</v>
+      </c>
+      <c r="G24" s="6">
+        <f>1/(D24*F24)</f>
+        <v>458.99999999999994</v>
+      </c>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6">
+        <f>D24*F24</f>
+        <v>2.1786492374727671E-3</v>
+      </c>
+      <c r="J24" s="6">
+        <f>1728*I24</f>
+        <v>3.7647058823529416</v>
+      </c>
+      <c r="K24" s="9">
+        <f>J24*9</f>
+        <v>33.882352941176471</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="7">
+        <v>1</v>
+      </c>
+      <c r="C25" s="7">
+        <v>1</v>
+      </c>
+      <c r="D25" s="7">
+        <f t="shared" ref="D25" si="6">(B25+C25)/2</f>
+        <v>1</v>
+      </c>
+      <c r="E25" s="7">
+        <v>5</v>
+      </c>
+      <c r="F25" s="8">
+        <f t="shared" ref="F25" si="7">E25/SUM(E$2:E$19)</f>
+        <v>1.0893246187363835E-2</v>
+      </c>
+      <c r="G25" s="6">
+        <f t="shared" ref="G25" si="8">1/(D25*F25)</f>
+        <v>91.8</v>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6">
+        <f>D25*F25</f>
+        <v>1.0893246187363835E-2</v>
+      </c>
+      <c r="J25" s="6">
+        <f t="shared" ref="J25" si="9">1728*I25</f>
+        <v>18.823529411764707</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" ref="K25" si="10">J25*9</f>
+        <v>169.41176470588235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="9"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="9"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="9"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="9"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="9"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="9"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="9"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="9"/>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="9"/>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="9"/>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="9"/>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="9"/>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="9"/>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/实体 entity/猪灵交易 1.16.2+.xlsx
+++ b/实体 entity/猪灵交易 1.16.2+.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\实体 entity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2DEB62-8388-4498-AE04-7C37647B6B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB400C91-C863-40F6-907C-FA3F3933DB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -628,7 +628,7 @@
         <v>10.199999999999999</v>
       </c>
       <c r="I2" s="6">
-        <f>D2*F2</f>
+        <f t="shared" ref="I2:I20" si="0">D2*F2</f>
         <v>1.0893246187363835E-2</v>
       </c>
       <c r="J2" s="6">
@@ -651,34 +651,34 @@
         <v>1</v>
       </c>
       <c r="D3" s="7">
-        <f t="shared" ref="D3:D20" si="0">(B3+C3)/2</f>
+        <f t="shared" ref="D3:D20" si="1">(B3+C3)/2</f>
         <v>1</v>
       </c>
       <c r="E3" s="7">
         <v>8</v>
       </c>
       <c r="F3" s="8">
-        <f t="shared" ref="F3:F20" si="1">E3/SUM(E$2:E$19)</f>
+        <f t="shared" ref="F3:F20" si="2">E3/SUM(E$2:E$19)</f>
         <v>1.7429193899782137E-2</v>
       </c>
       <c r="G3" s="6">
-        <f t="shared" ref="G3:G20" si="2">1/(D3*F3)</f>
+        <f t="shared" ref="G3:G20" si="3">1/(D3*F3)</f>
         <v>57.374999999999993</v>
       </c>
       <c r="H3" s="6">
-        <f t="shared" ref="H3:H20" si="3">G3/9</f>
+        <f t="shared" ref="H3:H20" si="4">G3/9</f>
         <v>6.3749999999999991</v>
       </c>
       <c r="I3" s="6">
-        <f>D3*F3</f>
+        <f t="shared" si="0"/>
         <v>1.7429193899782137E-2</v>
       </c>
       <c r="J3" s="6">
-        <f t="shared" ref="J3:J20" si="4">1728*I3</f>
+        <f t="shared" ref="J3:J20" si="5">1728*I3</f>
         <v>30.117647058823533</v>
       </c>
       <c r="K3" s="9">
-        <f t="shared" ref="K3:K20" si="5">J3*9</f>
+        <f t="shared" ref="K3:K20" si="6">J3*9</f>
         <v>271.05882352941177</v>
       </c>
     </row>
@@ -693,34 +693,34 @@
         <v>1</v>
       </c>
       <c r="D4" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E4" s="7">
         <v>8</v>
       </c>
       <c r="F4" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7429193899782137E-2</v>
       </c>
       <c r="G4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>57.374999999999993</v>
       </c>
       <c r="H4" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.3749999999999991</v>
       </c>
       <c r="I4" s="6">
-        <f>D4*F4</f>
+        <f t="shared" si="0"/>
         <v>1.7429193899782137E-2</v>
       </c>
       <c r="J4" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>30.117647058823533</v>
       </c>
       <c r="K4" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>271.05882352941177</v>
       </c>
     </row>
@@ -735,34 +735,34 @@
         <v>1</v>
       </c>
       <c r="D5" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E5" s="7">
         <v>8</v>
       </c>
       <c r="F5" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7429193899782137E-2</v>
       </c>
       <c r="G5" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>57.374999999999993</v>
       </c>
       <c r="H5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.3749999999999991</v>
       </c>
       <c r="I5" s="6">
-        <f>D5*F5</f>
+        <f t="shared" si="0"/>
         <v>1.7429193899782137E-2</v>
       </c>
       <c r="J5" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>30.117647058823533</v>
       </c>
       <c r="K5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>271.05882352941177</v>
       </c>
     </row>
@@ -777,34 +777,34 @@
         <v>1</v>
       </c>
       <c r="D6" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E6" s="7">
         <v>10</v>
       </c>
       <c r="F6" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.178649237472767E-2</v>
       </c>
       <c r="G6" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>45.9</v>
       </c>
       <c r="H6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.0999999999999996</v>
       </c>
       <c r="I6" s="6">
-        <f>D6*F6</f>
+        <f t="shared" si="0"/>
         <v>2.178649237472767E-2</v>
       </c>
       <c r="J6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>37.647058823529413</v>
       </c>
       <c r="K6" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>338.8235294117647</v>
       </c>
     </row>
@@ -819,34 +819,34 @@
         <v>36</v>
       </c>
       <c r="D7" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="E7" s="7">
         <v>10</v>
       </c>
       <c r="F7" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.178649237472767E-2</v>
       </c>
       <c r="G7" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.9956521739130433</v>
       </c>
       <c r="H7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.22173913043478258</v>
       </c>
       <c r="I7" s="6">
-        <f>D7*F7</f>
+        <f t="shared" si="0"/>
         <v>0.50108932461873645</v>
       </c>
       <c r="J7" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>865.88235294117658</v>
       </c>
       <c r="K7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7792.9411764705892</v>
       </c>
     </row>
@@ -861,34 +861,34 @@
         <v>4</v>
       </c>
       <c r="D8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="E8" s="7">
         <v>10</v>
       </c>
       <c r="F8" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.178649237472767E-2</v>
       </c>
       <c r="G8" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15.299999999999999</v>
       </c>
       <c r="H8" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.7</v>
       </c>
       <c r="I8" s="6">
-        <f>D8*F8</f>
+        <f t="shared" si="0"/>
         <v>6.535947712418301E-2</v>
       </c>
       <c r="J8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>112.94117647058825</v>
       </c>
       <c r="K8" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1016.4705882352943</v>
       </c>
     </row>
@@ -903,34 +903,34 @@
         <v>9</v>
       </c>
       <c r="D9" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="E9" s="7">
         <v>20</v>
       </c>
       <c r="F9" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.357298474945534E-2</v>
       </c>
       <c r="G9" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.8249999999999997</v>
       </c>
       <c r="H9" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="I9" s="6">
-        <f>D9*F9</f>
+        <f t="shared" si="0"/>
         <v>0.26143790849673204</v>
       </c>
       <c r="J9" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>451.76470588235298</v>
       </c>
       <c r="K9" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4065.882352941177</v>
       </c>
     </row>
@@ -945,34 +945,34 @@
         <v>12</v>
       </c>
       <c r="D10" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.5</v>
       </c>
       <c r="E10" s="7">
         <v>20</v>
       </c>
       <c r="F10" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.357298474945534E-2</v>
       </c>
       <c r="G10" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.6999999999999997</v>
       </c>
       <c r="H10" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.3</v>
       </c>
       <c r="I10" s="6">
-        <f>D10*F10</f>
+        <f t="shared" si="0"/>
         <v>0.37037037037037041</v>
       </c>
       <c r="J10" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>640.00000000000011</v>
       </c>
       <c r="K10" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5760.0000000000009</v>
       </c>
     </row>
@@ -987,34 +987,34 @@
         <v>1</v>
       </c>
       <c r="D11" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E11" s="7">
         <v>40</v>
       </c>
       <c r="F11" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.714596949891068E-2</v>
       </c>
       <c r="G11" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>11.475</v>
       </c>
       <c r="H11" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2749999999999999</v>
       </c>
       <c r="I11" s="6">
-        <f>D11*F11</f>
+        <f t="shared" si="0"/>
         <v>8.714596949891068E-2</v>
       </c>
       <c r="J11" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>150.58823529411765</v>
       </c>
       <c r="K11" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1355.2941176470588</v>
       </c>
     </row>
@@ -1029,34 +1029,34 @@
         <v>3</v>
       </c>
       <c r="D12" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E12" s="7">
         <v>40</v>
       </c>
       <c r="F12" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.714596949891068E-2</v>
       </c>
       <c r="G12" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.7374999999999998</v>
       </c>
       <c r="H12" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.63749999999999996</v>
       </c>
       <c r="I12" s="6">
-        <f>D12*F12</f>
+        <f t="shared" si="0"/>
         <v>0.17429193899782136</v>
       </c>
       <c r="J12" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>301.1764705882353</v>
       </c>
       <c r="K12" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2710.5882352941176</v>
       </c>
     </row>
@@ -1071,34 +1071,34 @@
         <v>1</v>
       </c>
       <c r="D13" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E13" s="7">
         <v>40</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.714596949891068E-2</v>
       </c>
       <c r="G13" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>11.475</v>
       </c>
       <c r="H13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2749999999999999</v>
       </c>
       <c r="I13" s="6">
-        <f>D13*F13</f>
+        <f t="shared" si="0"/>
         <v>8.714596949891068E-2</v>
       </c>
       <c r="J13" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>150.58823529411765</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1355.2941176470588</v>
       </c>
     </row>
@@ -1113,34 +1113,34 @@
         <v>4</v>
       </c>
       <c r="D14" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="E14" s="7">
         <v>40</v>
       </c>
       <c r="F14" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.714596949891068E-2</v>
       </c>
       <c r="G14" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.8249999999999997</v>
       </c>
       <c r="H14" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="I14" s="6">
-        <f>D14*F14</f>
+        <f t="shared" si="0"/>
         <v>0.26143790849673204</v>
       </c>
       <c r="J14" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>451.76470588235298</v>
       </c>
       <c r="K14" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4065.882352941177</v>
       </c>
     </row>
@@ -1155,34 +1155,34 @@
         <v>8</v>
       </c>
       <c r="D15" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="E15" s="7">
         <v>40</v>
       </c>
       <c r="F15" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.714596949891068E-2</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.2949999999999999</v>
       </c>
       <c r="H15" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.255</v>
       </c>
       <c r="I15" s="6">
-        <f>D15*F15</f>
+        <f t="shared" si="0"/>
         <v>0.4357298474945534</v>
       </c>
       <c r="J15" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>752.94117647058829</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6776.4705882352946</v>
       </c>
     </row>
@@ -1197,34 +1197,34 @@
         <v>8</v>
       </c>
       <c r="D16" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="E16" s="7">
         <v>40</v>
       </c>
       <c r="F16" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.714596949891068E-2</v>
       </c>
       <c r="G16" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.2949999999999999</v>
       </c>
       <c r="H16" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.255</v>
       </c>
       <c r="I16" s="6">
-        <f>D16*F16</f>
+        <f t="shared" si="0"/>
         <v>0.4357298474945534</v>
       </c>
       <c r="J16" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>752.94117647058829</v>
       </c>
       <c r="K16" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6776.4705882352946</v>
       </c>
     </row>
@@ -1239,34 +1239,34 @@
         <v>12</v>
       </c>
       <c r="D17" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="E17" s="7">
         <v>40</v>
       </c>
       <c r="F17" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.714596949891068E-2</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.2749999999999999</v>
       </c>
       <c r="H17" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.14166666666666666</v>
       </c>
       <c r="I17" s="6">
-        <f>D17*F17</f>
+        <f t="shared" si="0"/>
         <v>0.78431372549019618</v>
       </c>
       <c r="J17" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1355.294117647059</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12197.647058823532</v>
       </c>
     </row>
@@ -1281,34 +1281,34 @@
         <v>16</v>
       </c>
       <c r="D18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E18" s="7">
         <v>40</v>
       </c>
       <c r="F18" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.714596949891068E-2</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.95624999999999993</v>
       </c>
       <c r="H18" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.10625</v>
       </c>
       <c r="I18" s="6">
-        <f>D18*F18</f>
+        <f t="shared" si="0"/>
         <v>1.0457516339869282</v>
       </c>
       <c r="J18" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1807.0588235294119</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>16263.529411764708</v>
       </c>
     </row>
@@ -1323,34 +1323,34 @@
         <v>16</v>
       </c>
       <c r="D19" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E19" s="7">
         <v>40</v>
       </c>
       <c r="F19" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.714596949891068E-2</v>
       </c>
       <c r="G19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.95624999999999993</v>
       </c>
       <c r="H19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.10625</v>
       </c>
       <c r="I19" s="6">
-        <f>D19*F19</f>
+        <f t="shared" si="0"/>
         <v>1.0457516339869282</v>
       </c>
       <c r="J19" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1807.0588235294119</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>16263.529411764708</v>
       </c>
     </row>
@@ -1365,34 +1365,34 @@
         <v>1</v>
       </c>
       <c r="D20" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E20" s="7">
         <v>10</v>
       </c>
       <c r="F20" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.178649237472767E-2</v>
       </c>
       <c r="G20" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>45.9</v>
       </c>
       <c r="H20" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.0999999999999996</v>
       </c>
       <c r="I20" s="6">
-        <f>D20*F20</f>
+        <f t="shared" si="0"/>
         <v>2.178649237472767E-2</v>
       </c>
       <c r="J20" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>37.647058823529413</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>338.8235294117647</v>
       </c>
     </row>
@@ -1461,7 +1461,10 @@
         <f>1/(D24*F24)</f>
         <v>458.99999999999994</v>
       </c>
-      <c r="H24" s="6"/>
+      <c r="H24" s="6">
+        <f>G24/9</f>
+        <v>50.999999999999993</v>
+      </c>
       <c r="I24" s="6">
         <f>D24*F24</f>
         <v>2.1786492374727671E-3</v>
@@ -1486,31 +1489,34 @@
         <v>1</v>
       </c>
       <c r="D25" s="7">
-        <f t="shared" ref="D25" si="6">(B25+C25)/2</f>
+        <f t="shared" ref="D25" si="7">(B25+C25)/2</f>
         <v>1</v>
       </c>
       <c r="E25" s="7">
         <v>5</v>
       </c>
       <c r="F25" s="8">
-        <f t="shared" ref="F25" si="7">E25/SUM(E$2:E$19)</f>
+        <f t="shared" ref="F25" si="8">E25/SUM(E$2:E$19)</f>
         <v>1.0893246187363835E-2</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" ref="G25" si="8">1/(D25*F25)</f>
+        <f t="shared" ref="G25" si="9">1/(D25*F25)</f>
         <v>91.8</v>
       </c>
-      <c r="H25" s="6"/>
+      <c r="H25" s="6">
+        <f>G25/9</f>
+        <v>10.199999999999999</v>
+      </c>
       <c r="I25" s="6">
         <f>D25*F25</f>
         <v>1.0893246187363835E-2</v>
       </c>
       <c r="J25" s="6">
-        <f t="shared" ref="J25" si="9">1728*I25</f>
+        <f t="shared" ref="J25" si="10">1728*I25</f>
         <v>18.823529411764707</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" ref="K25" si="10">J25*9</f>
+        <f t="shared" ref="K25" si="11">J25*9</f>
         <v>169.41176470588235</v>
       </c>
     </row>
